--- a/data/data_xitu_LOOP3.xlsx
+++ b/data/data_xitu_LOOP3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xitu\code_literature\AL-SynAgent\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xitu\code_github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C17EEA-8624-4DAD-903B-8ADD85760F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC6E40A-1C9B-435E-94EB-71653CC27383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5685" yWindow="855" windowWidth="21240" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
